--- a/docs/ginza_first_36_episodes.xlsx
+++ b/docs/ginza_first_36_episodes.xlsx
@@ -86,7 +86,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -460,9 +460,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -474,7 +474,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>章｜月</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -499,22 +499,22 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1か月目｜見学と決意</t>
+          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>銀座のクラブ、見るだけでもいいですか？</t>
+          <t>見学だけでもいいですか？</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>応募ではなく店の見学を希望する主人公。銀座に興味はあるが、まだ働く覚悟まではない。</t>
+          <t>主人公は応募を決断できず、まず店を見に来る。</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>「憧れと迷いの中間」を入口に置き、視聴者に『自分も一度覗いてみたい』と思わせる。銀座への心理的ハードルを下げる。</t>
+          <t>応募という覚悟がなくても銀座に触れられる入口を示し、視聴者の『私には無理』というハードルを下げる。物語の起点。</t>
         </is>
       </c>
     </row>
@@ -522,9 +522,9 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>1か月目｜見学と決意</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>格式ある入口を見て怖くなり立ち去ろうとするが、藤澤さんに見つかる。</t>
+          <t>格式ある入口を前に、「私には無理」と逃げようとする。</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>銀座の格式・非日常性を示しつつ、『誰でも最初は怖い』という共感を生む。黒服＝安全な案内役という安心感も提示する。</t>
+          <t>『怖そう・ハードルが高そう』という不安に共感させつつ、逃げかけた主人公が留まる最初の転機を作る。</t>
         </is>
       </c>
     </row>
@@ -547,24 +547,24 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1か月目｜見学と決意</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>超美人しか働けないと思ってました</t>
+          <t>黒服って怖い人じゃないんですか？</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>営業前の店内で不安を口にする主人公に、藤澤さんは『顔だけで働ける場所なら、もっと簡単です』と答える。</t>
+          <t>藤澤さんと出会い、銀座への先入観が少し崩れる。</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>銀座は容姿だけの世界ではないという価値観を提示する。</t>
+          <t>黒服＝怖い/危険という先入観を崩し、藤澤さんを安心できる案内役として提示する。</t>
         </is>
       </c>
     </row>
@@ -572,24 +572,24 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1か月目｜見学と決意</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>私でも働けますか？</t>
+          <t>超美人しか働けないと思ってました</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>一番聞きたかった質問に、藤澤さんは『働くことはできる。でも、今のまま活躍できるとは言えない』と返す。</t>
+          <t>藤澤さんから、顔よりも所作・気遣い・信用を見る世界だと聞く。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>誰でも挑戦できるが成長が必要──『努力の余地＝希望』を示す。</t>
+          <t>『見た目が足りない』という不安に対し、銀座は容姿だけの世界ではないという価値観を提示する。</t>
         </is>
       </c>
     </row>
@@ -597,24 +597,24 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1か月目｜見学と決意</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素材はある。でも、そのままじゃ通用しない</t>
+          <t>私でも働けますか？</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>少し傷つきながらも、主人公は挑戦を決める。</t>
+          <t>藤澤さんは、働くことと活躍することは違うと伝える。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>物語の背骨『素材→魅力へ』を提示し、成長ストーリーの起点を作る。</t>
+          <t>『働ける』と『活躍できる』の違いを示し、努力の余地＝希望を提示する。</t>
         </is>
       </c>
     </row>
@@ -622,24 +622,24 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>1か月目｜見学と決意</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>銀座は、何を見ているんですか？</t>
+          <t>素材はある。でも今のままでは通用しない</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>藤澤さんが、外見・所作・言葉・気遣い・信用という評価基準を伝える。</t>
+          <t>主人公は傷つきながらも、挑戦を決める。</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>銀座の評価軸を言語化し、物語全体の指標を提示する。</t>
+          <t>物語の背骨『素材→魅力へ』を提示し、挑戦の決意という成長ストーリーの起点を作る。</t>
         </is>
       </c>
     </row>
@@ -649,22 +649,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2か月目｜垢抜けと店の中</t>
+          <t>第2章 最初の垢抜け｜2ヶ月目</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>高い服ならいいと思ってました</t>
+          <t>ドレスを着ても芋っぽい</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ブランド品を見せる主人公に、藤澤さんは値段と品格は別物だと伝える。</t>
+          <t>服を変えるだけでは銀座の女性に見えないと知る。</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>お金では品格は買えないという価値観を示す。</t>
+          <t>外見は服ではなく所作で決まると示し、『見た目に自信がなくても変われる』希望への布石を打つ。</t>
         </is>
       </c>
     </row>
@@ -672,24 +672,24 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2か月目｜垢抜けと店の中</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>第2章 最初の垢抜け｜2ヶ月目</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ドレスを着たのに、なぜか芋っぽい</t>
+          <t>かわいいって言われてきました</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>店内でドレス姿を確認する。原因は姿勢や表情にあると指摘される。</t>
+          <t>地元の基準と銀座の基準の違いを突きつけられる。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>外見は服ではなく所作で決まることを伝える。</t>
+          <t>これまでの成功体験が通用しない現実を描き、成長の必要性を突きつける。</t>
         </is>
       </c>
     </row>
@@ -697,9 +697,9 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2か月目｜垢抜けと店の中</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>第2章 最初の垢抜け｜2ヶ月目</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>猫背を直す練習を始める。髪や眉など日々の手入れも少しずつ整えていく。</t>
+          <t>外見より先に、姿勢と立ち方を直し始める。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>お金をかけずにできる最大の垢抜け＝姿勢・基礎の積み重ねだと伝える。</t>
+          <t>お金をかけずにできる最大の垢抜け＝姿勢を示し、誰でも今日から変われると伝える。</t>
         </is>
       </c>
     </row>
@@ -722,24 +722,24 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2か月目｜垢抜けと店の中</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>第2章 最初の垢抜け｜2ヶ月目</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>初めて自分を綺麗だと思えた</t>
+          <t>流行のメイクが似合わない</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>鏡の中の小さな変化に気づく。</t>
+          <t>自分の素材を消すのではなく、生かす方法を学ぶ。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>努力が実る最初の達成感を描き、視聴者に希望を持たせる。</t>
+          <t>流行に合わせるより自分の素材を生かすという主題を、外見の面で体現させる。</t>
         </is>
       </c>
     </row>
@@ -747,24 +747,24 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2か月目｜垢抜けと店の中</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>第2章 最初の垢抜け｜2ヶ月目</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>挨拶できない人は覚えてもらえない</t>
+          <t>笑えば何とかなると思ってました</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>先輩ホステスを前に固まる主人公。藤澤さんから、挨拶は売り込みではなく相手への敬意だと教わる。</t>
+          <t>緊張や無知を笑ってごまかす癖を直される。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>挨拶の本質＝敬意・信頼の第一歩であることを伝える。</t>
+          <t>表面的なごまかしをやめ、無知や緊張と正直に向き合う姿勢を促す。</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2か月目｜垢抜けと店の中</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>第2章 最初の垢抜け｜2ヶ月目</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>「なんか変わったね」</t>
+          <t>顔は同じなのに、少し綺麗に見える</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>座り方や声の使い方を直され、初めて先輩ホステスから声をかけられる。</t>
+          <t>髪、姿勢、表情の積み重ねで、最初の変化が現れる。</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>所作の細部が印象を決めること、そして努力が周囲に認められる喜びを描く。</t>
+          <t>積み重ねが生む最初の変化を可視化し、『変われるかもしれない』という視聴者の実感につなげる。</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>3か月目｜初めてのお客様と憧れ</t>
+          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>何を話せばいいか分からず、空回りする。</t>
+          <t>主人公は会話を盛り上げようとして空回りする。</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>接客の難しさとリアルな失敗を描く。</t>
+          <t>接客の難しさとリアルな失敗を描き、仕事内容への理解を始める。</t>
         </is>
       </c>
     </row>
@@ -822,24 +822,24 @@
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>3か月目｜初めてのお客様と憧れ</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>自分の話ばかりしてしまった</t>
+          <t>自分の話ばかりしていました</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>会話を盛り上げようとして、相手を見ていなかったと気づく。沈黙にも意味があると学ぶ。</t>
+          <t>接客は自分を見せることではなく、相手を見ることだと知る。</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>接客とは自分ではなく相手を見ることだと伝える。</t>
+          <t>接客の核心＝相手を見ることだと伝える。</t>
         </is>
       </c>
     </row>
@@ -847,24 +847,24 @@
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>3か月目｜初めてのお客様と憧れ</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>一流のお客様ほど静かだった</t>
+          <t>沈黙が怖くなくなった日</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>派手で威圧的という先入観が崩れる。席全体の空気を見る必要があると知る。</t>
+          <t>無理に話さない接客を覚える。</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>本物の品格は静けさにあり、仕事の奥行き＝全体を見る力だと示す。</t>
+          <t>間を恐れない余裕の価値を示す。</t>
         </is>
       </c>
     </row>
@@ -872,24 +872,24 @@
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>3か月目｜初めてのお客様と憧れ</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>初めて「また会いたい」と言われた</t>
+          <t>一流のお客様ほど静かだった</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>話術ではなく、相手の疲れに気づけたことで評価される。</t>
+          <t>怖い客ばかりという先入観が崩れる。</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>気配りが評価につながる──接客の核心を示す。</t>
+          <t>『危険そう』という不安を解消し、本物の品格は静けさにあると示す。</t>
         </is>
       </c>
     </row>
@@ -897,24 +897,24 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>3か月目｜初めてのお客様と憧れ</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>なぜ、あの人には全員が話したくなるの？</t>
+          <t>お酒を作るだけの仕事じゃない</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>エースホステスの接客を初めて見て、聞き方や気配りを観察する。</t>
+          <t>席全体の空気、先輩、黒服との連携を学ぶ。</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>目標となる存在を提示し、一流の技術を分析的に描く。</t>
+          <t>仕事の奥行きと、チームで働く安心感を伝える。</t>
         </is>
       </c>
     </row>
@@ -922,24 +922,24 @@
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>3か月目｜初めてのお客様と憧れ</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>その人になる必要はない</t>
+          <t>初めて「また会いたい」と言われた</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>エースを真似て失敗した主人公に、藤澤さんは自分の素材を使う必要があると指摘する。</t>
+          <t>元々持っていた観察力が、初めて仕事の武器になる。</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>表面的な模倣の限界を描き、『自分らしさを生かす』という主題を再確認する。</t>
+          <t>自分の素材を生かす主題を接客で結実させる。全体の折り返しで最初の評価を得る。</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>4か月目｜少し売れて、調子に乗る</t>
+          <t>第4章 売れ始めた女｜4ヶ月目</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>初めての指名</t>
+          <t>藤澤さんが言っていた女性</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>主人公が小さな成功を手にする。</t>
+          <t>主人公がファーストのエースを初めて間近で見る。</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>努力が結果に変わる喜びを描く。</t>
+          <t>エースを本格登場させ、目標となる存在を提示する。</t>
         </is>
       </c>
     </row>
@@ -972,24 +972,24 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>4か月目｜少し売れて、調子に乗る</t>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>第4章 売れ始めた女｜4ヶ月目</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>初めて自分のお金でドレスを買った</t>
+          <t>顔なら私も負けてないと思った</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>稼ぐ喜びと、女性としての自立を感じる。</t>
+          <t>主人公は外見で比較するが、存在感の差を見せつけられる。</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>経済的自立の第一歩を描く。</t>
+          <t>容姿と存在感は別物だと痛感させ、外見依存の限界を示す。</t>
         </is>
       </c>
     </row>
@@ -997,24 +997,24 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>4か月目｜少し売れて、調子に乗る</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>第4章 売れ始めた女｜4ヶ月目</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>お給料を全部美容に使いました</t>
+          <t>真似をしても全然違う</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>稼いだ分だけ使ってしまう未熟な金銭感覚を描く。</t>
+          <t>言葉や仕草だけをコピーし、接客に失敗する。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>成功の裏の落とし穴＝お金の使い方を提起する。</t>
+          <t>表面的な模倣の限界を描き、自分らしさの必要性を再確認させる。</t>
         </is>
       </c>
     </row>
@@ -1022,24 +1022,24 @@
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>4か月目｜少し売れて、調子に乗る</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>第4章 売れ始めた女｜4ヶ月目</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>お客様によって性格を変える</t>
+          <t>初めての指名</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>無邪気・知的・甘え上手など、相手に合わせて自分を演じ始める。</t>
+          <t>自分らしい接客によって、小さな成功を得る。</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>承認への依存と、自己を見失う兆候を描く。</t>
+          <t>努力が結果に変わる喜びを描く。全体の3分の2までに一度成功させる。</t>
         </is>
       </c>
     </row>
@@ -1047,24 +1047,24 @@
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>4か月目｜少し売れて、調子に乗る</t>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>第4章 売れ始めた女｜4ヶ月目</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>売れたら正解じゃないんですか？</t>
+          <t>最近、私かわいくないですか？</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>売上を唯一の基準にし始める。</t>
+          <t>売上と周囲の反応が変わり、少しずつ調子に乗る。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>数字至上主義への疑問を提起する。</t>
+          <t>承認と売上による慢心の芽を描く。</t>
         </is>
       </c>
     </row>
@@ -1072,9 +1072,9 @@
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>4か月目｜少し売れて、調子に乗る</t>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>第4章 売れ始めた女｜4ヶ月目</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>藤澤さんの言葉を、主人公は受け入れられない。</t>
+          <t>藤澤さんに本質を突かれるが、主人公は理解できない。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>成長の壁＝節目。売上と本当の価値の違いを問う。</t>
+          <t>売上と本当の価値の違いを突く節目。理解できない主人公で緊張を残す。</t>
         </is>
       </c>
     </row>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>5か月目｜信用・お金・安全</t>
+          <t>第5章 成功の代償｜5ヶ月目</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>こんなに使ってくれるなら信用していい？</t>
+          <t>太いお客様ができた</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>大きな金額を使う顧客がつき、金額と人間的信用は別物だと知る。</t>
+          <t>主人公の売上と生活が一気に華やかになる。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>お金≠人間的信用であることを伝える。</t>
+          <t>成功が一気に華やぐ場面で、次の崩壊への振り幅を作る。</t>
         </is>
       </c>
     </row>
@@ -1122,24 +1122,24 @@
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>5か月目｜信用・お金・安全</t>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>第5章 成功の代償｜5ヶ月目</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>払える人と、払う人は違う</t>
+          <t>こんなに使ってくれるなら信用していい？</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>掛け（売掛）と係の責任を学び、肩書や資産だけでは支払い意思を判断できないと知る。</t>
+          <t>金額と信用を混同し始める。</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>支払い意思を見抜く目と、売上に伴う責任を示す。</t>
+          <t>お金≠人間的信用という危うさを描く。</t>
         </is>
       </c>
     </row>
@@ -1147,24 +1147,24 @@
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>5か月目｜信用・お金・安全</t>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>第5章 成功の代償｜5ヶ月目</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>藤澤さんに止められた夜</t>
+          <t>他のお客様と会わないで</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>危険な判断をしようとし、藤澤さんに止められる。</t>
+          <t>顧客の独占欲が強くなり、主人公の自由が狭くなる。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>黒服の『守る』役割と、危機回避の重要性を描く。</t>
+          <t>依存関係の危うさを描く。</t>
         </is>
       </c>
     </row>
@@ -1172,24 +1172,24 @@
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>5か月目｜信用・お金・安全</t>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>第5章 成功の代償｜5ヶ月目</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>行かない方がいいお客様</t>
+          <t>売上を失うのが怖くて断れない</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>アフターの誘いを断る判断基準を知り、仕事とプライベートの境界を学ぶ。</t>
+          <t>自分を守るより、評価を優先してしまう。</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>自分を守る判断力と、境界線を持つことの大切さを伝える。</t>
+          <t>恐れが判断を歪め、自分を守れなくなる過程を描く。</t>
         </is>
       </c>
     </row>
@@ -1197,9 +1197,9 @@
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>5か月目｜信用・お金・安全</t>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>第5章 成功の代償｜5ヶ月目</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>主人公が裏引きの誘惑を受ける。</t>
+          <t>裏引きや危険な関係への誘惑を受ける。</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>目先の利益の誘惑とその危険を描く。</t>
+          <t>目先の利益の誘惑と危険を描き、『守ってくれる仕組みが必要』という視聴者心理につなげる。</t>
         </is>
       </c>
     </row>
@@ -1222,24 +1222,24 @@
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>5か月目｜信用・お金・安全</t>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>第5章 成功の代償｜5ヶ月目</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>ルールは女性を縛るためじゃない</t>
+          <t>私は魅力的になったんじゃなかった</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>店を通すことが信用と安全を守ることだと理解する。</t>
+          <t>売上や顧客を失い、「選ばれる技術」を魅力だと勘違いしていたことに気づく。</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ルールの意味＝女性を守る仕組みであると伝える。</t>
+          <t>崩壊の底＝転換点。魅力と『選ばれる技術』を取り違えていた過ちに気づかせる。</t>
         </is>
       </c>
     </row>
@@ -1249,22 +1249,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>6か月目｜崩壊と本当の垢抜け</t>
+          <t>第6章 本当の垢抜け｜6ヶ月目</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>売上を失うのが怖くて断れない</t>
+          <t>売れていない私には価値がない？</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>太客の要求が強くなり自由が狭まる中、自分を守るより評価を優先してしまう。</t>
+          <t>主人公は、売上に依存していた自分と向き合う。</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>依存関係の危うさと、恐れが判断を歪めることを描く。</t>
+          <t>売上に価値を預けていた自分を問い直す、再生の入口を描く。</t>
         </is>
       </c>
     </row>
@@ -1272,24 +1272,24 @@
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>6か月目｜崩壊と本当の垢抜け</t>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>第6章 本当の垢抜け｜6ヶ月目</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>私は作り物なんでしょうか</t>
+          <t>助けを求めることは負けじゃない</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>外見も接客も、誰かに選ばれるために作ったものだと感じる。</t>
+          <t>藤澤さんや先輩に、自分の失敗を正直に相談する。</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>アイデンティティの危機を描く。</t>
+          <t>頼ることの強さと、一人で抱えず店に相談できる仕組みを伝える。</t>
         </is>
       </c>
     </row>
@@ -1297,24 +1297,24 @@
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>6か月目｜崩壊と本当の垢抜け</t>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>第6章 本当の垢抜け｜6ヶ月目</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>売れていない私には価値がない？</t>
+          <t>初めてお客様に断った</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>顧客が離れ成功が崩れる。藤澤さんは答えを教えず、主人公自身に考えさせる。</t>
+          <t>相手の機嫌ではなく、自分の境界線を守る。</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>成功の崩壊＝どん底で、自分の価値を自ら問い直す転機を作る。</t>
+          <t>品格ある自己主張＝境界線を守る力の確立を描く。</t>
         </is>
       </c>
     </row>
@@ -1322,24 +1322,24 @@
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>6か月目｜崩壊と本当の垢抜け</t>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>第6章 本当の垢抜け｜6ヶ月目</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>無理に笑うのをやめました</t>
+          <t>断っても戻ってきてくれた</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>すべての客に好かれようとするのをやめ、知らないことは知らないと言え、品を保って断れるようになる。</t>
+          <t>自立した態度が、長期的な信用につながると知る。</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>『自分軸』と品格ある自己主張の確立を描く。</t>
+          <t>自立の報酬──媚びない態度こそが本当の信用を生むと示す。</t>
         </is>
       </c>
     </row>
@@ -1347,24 +1347,24 @@
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>6か月目｜崩壊と本当の垢抜け</t>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>第6章 本当の垢抜け｜6ヶ月目</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>新人が見学に来た──私でも働けますか？</t>
+          <t>新人が見学に来た</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>かつての自分と同じ未経験女性が店を訪れる。その質問に一年前の自分を重ね、主人公は『今のままでは難しい。でも、ここで変わることはできるよ』と答える。</t>
+          <t>かつての主人公と同じ不安を持つ未経験女性が現れる。</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>成長の証。第1話と対をなす円環構造で、変化を際立たせる。</t>
+          <t>物語の継承を始める。第1話と対をなし、主人公の変化を際立たせる。</t>
         </is>
       </c>
     </row>
@@ -1372,9 +1372,9 @@
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>6か月目｜崩壊と本当の垢抜け</t>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>第6章 本当の垢抜け｜6ヶ月目</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>新人を店内へ案内する主人公に、藤澤さんが『最初に言ったよな。素材はあるって』『やっと、自分の魅力にできたな』と言う。主人公は静かに笑い、店の扉を開く。</t>
+          <t>新人から『私でも働けますか？』と聞かれ、主人公は『今のままでは難しい。でも、ここで変わることはできるよ』と答え、店内へ案内する。藤澤さんは『やっと、素材を自分の魅力にできたな』と言う。</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>物語の結実＝素材が魅力へ。視聴者に『一度、銀座ファーストを見に行ってみたい』と思わせる着地。</t>
+          <t>物語の結実＝素材が魅力へ。視聴者に『一度、見学に行ってみたい』と思わせる着地。</t>
         </is>
       </c>
     </row>

--- a/docs/ginza_first_36_episodes.xlsx
+++ b/docs/ginza_first_36_episodes.xlsx
@@ -10,7 +10,7 @@
     <sheet name="銀座ファースト36本" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'銀座ファースト36本'!$A$1:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'銀座ファースト36本'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,7 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2E9DE"/>
+        <fgColor rgb="00FBF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2DEDE"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -86,6 +91,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,14 +464,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,20 +483,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>章｜月</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>章（PDFストーリー構造）</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>企画タイトル</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>目的・意図（何を伝えたいか）</t>
         </is>
@@ -499,20 +513,25 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
+          <t>1ヶ月目</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>第1章 私は通用すると思っていた（銀座の現実を知る）</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
           <t>見学だけでもいいですか？</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>主人公は応募を決断できず、まず店を見に来る。</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>応募という覚悟がなくても銀座に触れられる入口を示し、視聴者の『私には無理』というハードルを下げる。物語の起点。</t>
         </is>
@@ -522,22 +541,27 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1ヶ月目</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>第1章 私は通用すると思っていた（銀座の現実を知る）</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>扉の前で帰ろうとした</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>格式ある入口を前に、「私には無理」と逃げようとする。</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>『怖そう・ハードルが高そう』という不安に共感させつつ、逃げかけた主人公が留まる最初の転機を作る。</t>
         </is>
@@ -547,22 +571,27 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1ヶ月目</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>第1章 私は通用すると思っていた（銀座の現実を知る）</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>黒服って怖い人じゃないんですか？</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>藤澤さんと出会い、銀座への先入観が少し崩れる。</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>黒服＝怖い/危険という先入観を崩し、藤澤さんを安心できる案内役として提示する。</t>
         </is>
@@ -572,22 +601,27 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1ヶ月目</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>第1章 私は通用すると思っていた（銀座の現実を知る）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>超美人しか働けないと思ってました</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>藤澤さんから、顔よりも所作・気遣い・信用を見る世界だと聞く。</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>『見た目が足りない』という不安に対し、銀座は容姿だけの世界ではないという価値観を提示する。</t>
         </is>
@@ -597,22 +631,27 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1ヶ月目</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>第1章 私は通用すると思っていた（銀座の現実を知る）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>私でも働けますか？</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>藤澤さんは、働くことと活躍することは違うと伝える。</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>『働ける』と『活躍できる』の違いを示し、努力の余地＝希望を提示する。</t>
         </is>
@@ -622,24 +661,29 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>第1章 銀座ファーストを知る｜1ヶ月目</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1ヶ月目</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>第1章 私は通用すると思っていた（銀座の現実を知る）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>素材はある。でも今のままでは通用しない</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>主人公は傷つきながらも、挑戦を決める。</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>物語の背骨『素材→魅力へ』を提示し、挑戦の決意という成長ストーリーの起点を作る。</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>『私は通用すると思っていた』という思い込みが崩れ、素材→魅力へという成長ストーリーの起点＝挑戦の決意を描く。</t>
         </is>
       </c>
     </row>
@@ -649,20 +693,25 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>第2章 最初の垢抜け｜2ヶ月目</t>
+          <t>2ヶ月目</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
           <t>ドレスを着ても芋っぽい</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>服を変えるだけでは銀座の女性に見えないと知る。</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>外見は服ではなく所作で決まると示し、『見た目に自信がなくても変われる』希望への布石を打つ。</t>
         </is>
@@ -672,22 +721,27 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>第2章 最初の垢抜け｜2ヶ月目</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2ヶ月目</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>かわいいって言われてきました</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>地元の基準と銀座の基準の違いを突きつけられる。</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>これまでの成功体験が通用しない現実を描き、成長の必要性を突きつける。</t>
         </is>
@@ -697,22 +751,27 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>第2章 最初の垢抜け｜2ヶ月目</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2ヶ月目</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>姿勢が一番安いドレス</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>外見より先に、姿勢と立ち方を直し始める。</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>お金をかけずにできる最大の垢抜け＝姿勢を示し、誰でも今日から変われると伝える。</t>
         </is>
@@ -722,22 +781,27 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>第2章 最初の垢抜け｜2ヶ月目</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2ヶ月目</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>流行のメイクが似合わない</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>自分の素材を消すのではなく、生かす方法を学ぶ。</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>流行に合わせるより自分の素材を生かすという主題を、外見の面で体現させる。</t>
         </is>
@@ -747,22 +811,27 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>第2章 最初の垢抜け｜2ヶ月目</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2ヶ月目</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>笑えば何とかなると思ってました</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>緊張や無知を笑ってごまかす癖を直される。</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>表面的なごまかしをやめ、無知や緊張と正直に向き合う姿勢を促す。</t>
         </is>
@@ -772,24 +841,29 @@
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>第2章 最初の垢抜け｜2ヶ月目</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2ヶ月目</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>顔は同じなのに、少し綺麗に見える</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>髪、姿勢、表情の積み重ねで、最初の変化が現れる。</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>積み重ねが生む最初の変化を可視化し、『変われるかもしれない』という視聴者の実感につなげる。</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>積み重ねが生む最初の変化を可視化し、『変われるかもしれない』という視聴者の実感につなげる（垢抜け＝外見の完成）。</t>
         </is>
       </c>
     </row>
@@ -799,22 +873,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+          <t>3ヶ月目</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>初めて席についた日</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>主人公は会話を盛り上げようとして空回りする。</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>接客の難しさとリアルな失敗を描き、仕事内容への理解を始める。</t>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>接客の難しさとリアルな失敗を描き、銀座ファーストの仕事＝文化への理解を始める。</t>
         </is>
       </c>
     </row>
@@ -822,22 +901,27 @@
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>3ヶ月目</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>自分の話ばかりしていました</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>接客は自分を見せることではなく、相手を見ることだと知る。</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>接客の核心＝相手を見ることだと伝える。</t>
         </is>
@@ -847,22 +931,27 @@
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>3ヶ月目</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>沈黙が怖くなくなった日</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>無理に話さない接客を覚える。</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>間を恐れない余裕の価値を示す。</t>
         </is>
@@ -872,22 +961,27 @@
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>3ヶ月目</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>一流のお客様ほど静かだった</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>怖い客ばかりという先入観が崩れる。</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>『危険そう』という不安を解消し、本物の品格は静けさにあると示す。</t>
         </is>
@@ -897,24 +991,29 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>3ヶ月目</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>お酒を作るだけの仕事じゃない</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>席全体の空気、先輩、黒服との連携を学ぶ。</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>仕事の奥行きと、チームで働く安心感を伝える。</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>仕事の奥行きと、チームで働く安心感＝店の文化を伝える。</t>
         </is>
       </c>
     </row>
@@ -922,22 +1021,27 @@
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>第3章 銀座の仕事を知る｜3ヶ月目</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>3ヶ月目</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>第2章 努力して少しずつ垢抜ける（銀座ファーストという文化を知る）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>初めて「また会いたい」と言われた</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>元々持っていた観察力が、初めて仕事の武器になる。</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>自分の素材を生かす主題を接客で結実させる。全体の折り返しで最初の評価を得る。</t>
         </is>
@@ -949,20 +1053,25 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>第4章 売れ始めた女｜4ヶ月目</t>
+          <t>4ヶ月目</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>第3章 売れ始める（「魅力＝売れること」だと勘違いする）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
           <t>藤澤さんが言っていた女性</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>主人公がファーストのエースを初めて間近で見る。</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>エースを本格登場させ、目標となる存在を提示する。</t>
         </is>
@@ -972,22 +1081,27 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>第4章 売れ始めた女｜4ヶ月目</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>4ヶ月目</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>第3章 売れ始める（「魅力＝売れること」だと勘違いする）</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>顔なら私も負けてないと思った</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>主人公は外見で比較するが、存在感の差を見せつけられる。</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>容姿と存在感は別物だと痛感させ、外見依存の限界を示す。</t>
         </is>
@@ -997,22 +1111,27 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>第4章 売れ始めた女｜4ヶ月目</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>4ヶ月目</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>第3章 売れ始める（「魅力＝売れること」だと勘違いする）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>真似をしても全然違う</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>言葉や仕草だけをコピーし、接客に失敗する。</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>表面的な模倣の限界を描き、自分らしさの必要性を再確認させる。</t>
         </is>
@@ -1022,22 +1141,27 @@
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>第4章 売れ始めた女｜4ヶ月目</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>4ヶ月目</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>第3章 売れ始める（「魅力＝売れること」だと勘違いする）</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>初めての指名</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>自分らしい接客によって、小さな成功を得る。</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>努力が結果に変わる喜びを描く。全体の3分の2までに一度成功させる。</t>
         </is>
@@ -1047,24 +1171,29 @@
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>第4章 売れ始めた女｜4ヶ月目</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>4ヶ月目</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>第3章 売れ始める（「魅力＝売れること」だと勘違いする）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>最近、私かわいくないですか？</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>売上と周囲の反応が変わり、少しずつ調子に乗る。</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>承認と売上による慢心の芽を描く。</t>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>承認と売上による慢心の芽＝『魅力＝売れること』という勘違いの始まりを描く。</t>
         </is>
       </c>
     </row>
@@ -1072,22 +1201,27 @@
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>第4章 売れ始めた女｜4ヶ月目</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>4ヶ月目</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>第3章 売れ始める（「魅力＝売れること」だと勘違いする）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>今のお前は、売れてるだけ</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>藤澤さんに本質を突かれるが、主人公は理解できない。</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>売上と本当の価値の違いを突く節目。理解できない主人公で緊張を残す。</t>
         </is>
@@ -1099,20 +1233,25 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>第5章 成功の代償｜5ヶ月目</t>
+          <t>5ヶ月目</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
+          <t>第4章 成功の代償（自分を見失う）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
           <t>太いお客様ができた</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>主人公の売上と生活が一気に華やかになる。</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>成功が一気に華やぐ場面で、次の崩壊への振り幅を作る。</t>
         </is>
@@ -1122,22 +1261,27 @@
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>第5章 成功の代償｜5ヶ月目</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>5ヶ月目</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>第4章 成功の代償（自分を見失う）</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>こんなに使ってくれるなら信用していい？</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>金額と信用を混同し始める。</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>お金≠人間的信用という危うさを描く。</t>
         </is>
@@ -1147,22 +1291,27 @@
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>第5章 成功の代償｜5ヶ月目</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>5ヶ月目</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>第4章 成功の代償（自分を見失う）</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>他のお客様と会わないで</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>顧客の独占欲が強くなり、主人公の自由が狭くなる。</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>依存関係の危うさを描く。</t>
         </is>
@@ -1172,22 +1321,27 @@
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>第5章 成功の代償｜5ヶ月目</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>5ヶ月目</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>第4章 成功の代償（自分を見失う）</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>売上を失うのが怖くて断れない</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>自分を守るより、評価を優先してしまう。</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>恐れが判断を歪め、自分を守れなくなる過程を描く。</t>
         </is>
@@ -1197,22 +1351,27 @@
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>第5章 成功の代償｜5ヶ月目</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>5ヶ月目</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>第4章 成功の代償（自分を見失う）</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>店を通さない方が稼げるよ</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>裏引きや危険な関係への誘惑を受ける。</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>目先の利益の誘惑と危険を描き、『守ってくれる仕組みが必要』という視聴者心理につなげる。</t>
         </is>
@@ -1222,24 +1381,29 @@
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>第5章 成功の代償｜5ヶ月目</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>5ヶ月目</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>第4章 成功の代償（自分を見失う）</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>私は魅力的になったんじゃなかった</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>売上や顧客を失い、「選ばれる技術」を魅力だと勘違いしていたことに気づく。</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>崩壊の底＝転換点。魅力と『選ばれる技術』を取り違えていた過ちに気づかせる。</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>成功の代償＝自分を見失った底。魅力と『選ばれる技術』を取り違えていた過ちに気づかせる。</t>
         </is>
       </c>
     </row>
@@ -1249,22 +1413,27 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>第6章 本当の垢抜け｜6ヶ月目</t>
+          <t>6ヶ月目</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
+          <t>第5章 本当の魅力を知る（人として成長する）</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
           <t>売れていない私には価値がない？</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>主人公は、売上に依存していた自分と向き合う。</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>売上に価値を預けていた自分を問い直す、再生の入口を描く。</t>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>売上に価値を預けていた自分を問い直す、本当の魅力に気づく再生の入口を描く。</t>
         </is>
       </c>
     </row>
@@ -1272,24 +1441,29 @@
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>第6章 本当の垢抜け｜6ヶ月目</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>6ヶ月目</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>第5章 本当の魅力を知る（人として成長する）</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>助けを求めることは負けじゃない</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>藤澤さんや先輩に、自分の失敗を正直に相談する。</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>頼ることの強さと、一人で抱えず店に相談できる仕組みを伝える。</t>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>頼ることの強さと、一人で抱えず店に相談できる仕組みを伝える（人として成長）。</t>
         </is>
       </c>
     </row>
@@ -1297,24 +1471,29 @@
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>第6章 本当の垢抜け｜6ヶ月目</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>6ヶ月目</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>第5章 本当の魅力を知る（人として成長する）</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>初めてお客様に断った</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>相手の機嫌ではなく、自分の境界線を守る。</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>品格ある自己主張＝境界線を守る力の確立を描く。</t>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>品格ある自己主張＝境界線を守る力の確立を描く（人として成長）。</t>
         </is>
       </c>
     </row>
@@ -1322,24 +1501,29 @@
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>第6章 本当の垢抜け｜6ヶ月目</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>6ヶ月目</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>第6章 自分らしく活躍できる女性になる（新人へバトンを渡す）</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
           <t>断っても戻ってきてくれた</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>自立した態度が、長期的な信用につながると知る。</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>自立の報酬──媚びない態度こそが本当の信用を生むと示す。</t>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>自立の報酬──媚びない態度こそが本当の信用を生むと示す（自分らしく活躍する女性へ）。</t>
         </is>
       </c>
     </row>
@@ -1347,24 +1531,29 @@
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>第6章 本当の垢抜け｜6ヶ月目</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>6ヶ月目</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>第6章 自分らしく活躍できる女性になる（新人へバトンを渡す）</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>新人が見学に来た</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>かつての主人公と同じ不安を持つ未経験女性が現れる。</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>物語の継承を始める。第1話と対をなし、主人公の変化を際立たせる。</t>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>物語の継承＝新人へバトンを渡す始まり。第1話と対をなし、主人公の変化を際立たせる。</t>
         </is>
       </c>
     </row>
@@ -1372,29 +1561,34 @@
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>第6章 本当の垢抜け｜6ヶ月目</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>6ヶ月目</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>第6章 自分らしく活躍できる女性になる（新人へバトンを渡す）</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>素材が魅力になった日</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>新人から『私でも働けますか？』と聞かれ、主人公は『今のままでは難しい。でも、ここで変わることはできるよ』と答え、店内へ案内する。藤澤さんは『やっと、素材を自分の魅力にできたな』と言う。</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>物語の結実＝素材が魅力へ。視聴者に『一度、見学に行ってみたい』と思わせる着地。</t>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>物語の結実＝素材が魅力へ。新人へバトンを渡し、視聴者に『一度、見学に行ってみたい』と思わせる着地。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E37"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>